--- a/aula03 excel/atividade Trimestral.xlsx
+++ b/aula03 excel/atividade Trimestral.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aluno\Documents\GitHub\karlos henrique\aula03 excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D307DDD-B05F-437F-8B93-0A723EBD5361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D71FF0DC-1976-4153-B241-3175AF01F880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="2" activeTab="2" xr2:uid="{C68FDCCB-B8FC-4987-A0C8-AC903749D8A8}"/>
+    <workbookView xWindow="2985" yWindow="1185" windowWidth="16035" windowHeight="11295" xr2:uid="{C68FDCCB-B8FC-4987-A0C8-AC903749D8A8}"/>
   </bookViews>
   <sheets>
     <sheet name="Atividade Trimestral 1" sheetId="3" r:id="rId1"/>
@@ -210,7 +210,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -221,21 +221,20 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -561,47 +560,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
     </row>
     <row r="3" spans="1:7" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="9" t="s">
+      <c r="E3" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="14" t="s">
         <v>9</v>
       </c>
     </row>
@@ -609,12 +608,12 @@
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -828,8 +827,8 @@
         <v>0</v>
       </c>
       <c r="G13" s="4">
-        <f t="shared" si="0"/>
-        <v>8.6875</v>
+        <f>AVERAGE(B13:F13)</f>
+        <v>6.95</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -837,7 +836,7 @@
         <v>19</v>
       </c>
       <c r="B15" s="6">
-        <f>SUM(F5:F12)</f>
+        <f>SUM(F5:F13)</f>
         <v>35</v>
       </c>
     </row>
@@ -890,47 +889,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
     </row>
     <row r="3" spans="1:7" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="9" t="s">
+      <c r="E3" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="14" t="s">
         <v>9</v>
       </c>
     </row>
@@ -938,12 +937,12 @@
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -1219,47 +1218,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
     </row>
     <row r="3" spans="1:7" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="9" t="s">
+      <c r="E3" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="14" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1267,12 +1266,12 @@
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -1551,56 +1550,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="8" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
+      <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="16">
+      <c r="B4" s="12">
         <f>'Atividade Trimestral 1'!G5</f>
         <v>6.125</v>
       </c>
-      <c r="C4" s="16">
+      <c r="C4" s="12">
         <f>'Atividade Trimestral (2)'!G5</f>
         <v>5.75</v>
       </c>
@@ -1612,24 +1611,24 @@
         <f>'Atividade Trimestral 1'!F5+'Atividade Trimestral (2)'!F5+'Atividade Trimestral (3)'!F5</f>
         <v>42</v>
       </c>
-      <c r="F4" s="16">
+      <c r="F4" s="12">
         <f>AVERAGE(B4:D4)</f>
         <v>5.458333333333333</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
+      <c r="A5" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="16">
+      <c r="B5" s="12">
         <f>'Atividade Trimestral 1'!G6</f>
         <v>5.375</v>
       </c>
-      <c r="C5" s="16">
+      <c r="C5" s="12">
         <f>'Atividade Trimestral (2)'!G6</f>
         <v>6.75</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="12">
         <f>'Atividade Trimestral (3)'!G6</f>
         <v>7</v>
       </c>
@@ -1637,24 +1636,24 @@
         <f>'Atividade Trimestral 1'!F6+'Atividade Trimestral (2)'!F6+'Atividade Trimestral (3)'!F6</f>
         <v>14</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="12">
         <f t="shared" ref="F5:F12" si="0">AVERAGE(B5:D5)</f>
         <v>6.375</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
+      <c r="A6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="12">
         <f>'Atividade Trimestral 1'!G7</f>
         <v>6.6875</v>
       </c>
-      <c r="C6" s="16">
+      <c r="C6" s="12">
         <f>'Atividade Trimestral (2)'!G7</f>
         <v>7.25</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="12">
         <f>'Atividade Trimestral (3)'!G7</f>
         <v>6.6875</v>
       </c>
@@ -1662,24 +1661,24 @@
         <f>'Atividade Trimestral 1'!F7+'Atividade Trimestral (2)'!F7+'Atividade Trimestral (3)'!F7</f>
         <v>11</v>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="12">
         <f t="shared" si="0"/>
         <v>6.875</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
+      <c r="A7" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="16">
+      <c r="B7" s="12">
         <f>'Atividade Trimestral 1'!G8</f>
         <v>6.8375000000000004</v>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="12">
         <f>'Atividade Trimestral (2)'!G8</f>
         <v>7.0625</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="12">
         <f>'Atividade Trimestral (3)'!G8</f>
         <v>6.8125</v>
       </c>
@@ -1687,24 +1686,24 @@
         <f>'Atividade Trimestral 1'!F8+'Atividade Trimestral (2)'!F8+'Atividade Trimestral (3)'!F8</f>
         <v>2</v>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="12">
         <f t="shared" si="0"/>
         <v>6.9041666666666659</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+      <c r="A8" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="16">
+      <c r="B8" s="12">
         <f>'Atividade Trimestral 1'!G9</f>
         <v>7.9375</v>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="12">
         <f>'Atividade Trimestral (2)'!G9</f>
         <v>7.0625</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="12">
         <f>'Atividade Trimestral (3)'!G9</f>
         <v>7.9375</v>
       </c>
@@ -1712,24 +1711,24 @@
         <f>'Atividade Trimestral 1'!F9+'Atividade Trimestral (2)'!F9+'Atividade Trimestral (3)'!F9</f>
         <v>1</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="12">
         <f t="shared" si="0"/>
         <v>7.645833333333333</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
+      <c r="A9" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="16">
+      <c r="B9" s="12">
         <f>'Atividade Trimestral 1'!G10</f>
         <v>9.0625</v>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="12">
         <f>'Atividade Trimestral (2)'!G10</f>
         <v>7.5</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="12">
         <f>'Atividade Trimestral (3)'!G10</f>
         <v>9.0625</v>
       </c>
@@ -1737,24 +1736,24 @@
         <f>'Atividade Trimestral 1'!F10+'Atividade Trimestral (2)'!F10+'Atividade Trimestral (3)'!F10</f>
         <v>4</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="12">
         <f t="shared" si="0"/>
         <v>8.5416666666666661</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
+      <c r="A10" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="16">
+      <c r="B10" s="12">
         <f>'Atividade Trimestral 1'!G11</f>
         <v>8.375</v>
       </c>
-      <c r="C10" s="16">
+      <c r="C10" s="12">
         <f>'Atividade Trimestral (2)'!G11</f>
         <v>7.25</v>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="12">
         <f>'Atividade Trimestral (3)'!G11</f>
         <v>9</v>
       </c>
@@ -1762,24 +1761,24 @@
         <f>'Atividade Trimestral 1'!F11+'Atividade Trimestral (2)'!F11+'Atividade Trimestral (3)'!F11</f>
         <v>0</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="12">
         <f t="shared" si="0"/>
         <v>8.2083333333333339</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
+      <c r="A11" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="16">
+      <c r="B11" s="12">
         <f>'Atividade Trimestral 1'!G12</f>
         <v>7.8125</v>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="12">
         <f>'Atividade Trimestral (2)'!G12</f>
         <v>7.875</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="12">
         <f>'Atividade Trimestral (3)'!G12</f>
         <v>7.8125</v>
       </c>
@@ -1787,24 +1786,24 @@
         <f>'Atividade Trimestral 1'!F12+'Atividade Trimestral (2)'!F12+'Atividade Trimestral (3)'!F12</f>
         <v>6</v>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="12">
         <f t="shared" si="0"/>
         <v>7.833333333333333</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
+      <c r="A12" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="16">
+      <c r="B12" s="12">
         <f>'Atividade Trimestral 1'!G13</f>
-        <v>8.6875</v>
-      </c>
-      <c r="C12" s="16">
+        <v>6.95</v>
+      </c>
+      <c r="C12" s="12">
         <f>'Atividade Trimestral (2)'!G13</f>
         <v>7.625</v>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="12">
         <f>'Atividade Trimestral (3)'!G13</f>
         <v>8.6875</v>
       </c>
@@ -1812,23 +1811,23 @@
         <f>'Atividade Trimestral 1'!F13+'Atividade Trimestral (2)'!F13+'Atividade Trimestral (3)'!F13</f>
         <v>0</v>
       </c>
-      <c r="F12" s="16">
-        <f t="shared" si="0"/>
-        <v>8.3333333333333339</v>
+      <c r="F12" s="12">
+        <f t="shared" si="0"/>
+        <v>7.7541666666666664</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="13"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="14" t="s">
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E13" s="15">
+      <c r="E13" s="11">
         <f>E4+E5+E6+E7+E8+E9+E10+E11+E12</f>
         <v>80</v>
       </c>
-      <c r="F13" s="13"/>
+      <c r="F13" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/aula03 excel/atividade Trimestral.xlsx
+++ b/aula03 excel/atividade Trimestral.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aluno\Documents\GitHub\karlos henrique\aula03 excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D71FF0DC-1976-4153-B241-3175AF01F880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FE00C53-B166-4C51-BEB4-B736E71E23AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2985" yWindow="1185" windowWidth="16035" windowHeight="11295" xr2:uid="{C68FDCCB-B8FC-4987-A0C8-AC903749D8A8}"/>
+    <workbookView xWindow="2985" yWindow="1185" windowWidth="16035" windowHeight="11295" firstSheet="1" activeTab="2" xr2:uid="{C68FDCCB-B8FC-4987-A0C8-AC903749D8A8}"/>
   </bookViews>
   <sheets>
     <sheet name="Atividade Trimestral 1" sheetId="3" r:id="rId1"/>
@@ -659,7 +659,7 @@
         <v>6</v>
       </c>
       <c r="G6" s="4">
-        <f t="shared" ref="G6:G13" si="0">AVERAGE(B6:E6)</f>
+        <f t="shared" ref="G6:G12" si="0">AVERAGE(B6:E6)</f>
         <v>5.375</v>
       </c>
     </row>
@@ -1165,7 +1165,7 @@
         <v>19</v>
       </c>
       <c r="B15" s="6">
-        <f>SUM(F5:F12)</f>
+        <f>SUM(F5:F13)</f>
         <v>36</v>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
         <v>19</v>
       </c>
       <c r="B15" s="6">
-        <f>SUM(F5:F12)</f>
+        <f>SUM(F5:F13)</f>
         <v>9</v>
       </c>
     </row>
